--- a/example/contacts.xlsx
+++ b/example/contacts.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,88 +459,132 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Marilyn Jackson</t>
+          <t>Teresa Martin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>scotiow28+MarilynJackson@gmail.com</t>
+          <t>TeresaMartin@email.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Marilyn Jackson</t>
+          <t>Teresa Martin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>scotiow28+MarilynJackson@gmail.com</t>
+          <t>TeresaMartin@email.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Charles Lee</t>
+          <t>Danielle Ray</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>scotiow28+CharlesLee@gmail.com</t>
+          <t>DanielleRay@email.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charles Lee</t>
+          <t>Danielle Ray</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>scotiow28+CharlesLee@gmail.com</t>
+          <t>DanielleRay@email.com</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Jason Alvarez</t>
+          <t>Seth Johnson</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>scotiow28+JasonAlvarez@gmail.com</t>
+          <t>SethJohnson@email.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jason Alvarez</t>
+          <t>Seth Johnson</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>scotiow28+JasonAlvarez@gmail.com</t>
+          <t>SethJohnson@email.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>William Perry</t>
+          <t>David Harding</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>scotiow28+WilliamPerry@gmail.com</t>
+          <t>DavidHarding@email.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>William Perry</t>
+          <t>David Harding</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>scotiow28+WilliamPerry@gmail.com</t>
+          <t>DavidHarding@email.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Courtney Greene</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CourtneyGreene@email.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Courtney Greene</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CourtneyGreene@email.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Jennifer Fleming</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JenniferFleming@email.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jennifer Fleming</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>JenniferFleming@email.com</t>
         </is>
       </c>
     </row>
@@ -555,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,7 +610,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>End Date</t>
         </is>
       </c>
     </row>
@@ -575,7 +624,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45788</v>
+        <v>45837</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>45851</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +635,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45802</v>
+        <v>45851</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>45865</v>
       </c>
     </row>
     <row r="4">
@@ -591,7 +646,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45816</v>
+        <v>45865</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>45879</v>
       </c>
     </row>
     <row r="5">
@@ -599,7 +657,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45830</v>
+        <v>45879</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>45893</v>
       </c>
     </row>
     <row r="6">
@@ -607,23 +668,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45844</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45858</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45872</v>
+        <v>45893</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>45907</v>
       </c>
     </row>
   </sheetData>
